--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-machine-execution-audit-event.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-machine-execution-audit-event.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Machine Execution Audit Event</t>
+    <t>EU AI Execution Audit Event</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Logs the automated execution of an AI model, establishing the core traceability chain.</t>
+    <t>An AuditEvent profile documenting execution-related metadata of an AI-supported processing event to support retrospective reconstruction and auditability.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -7760,7 +7760,7 @@
         <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>18</v>
@@ -11349,7 +11349,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>505</v>
       </c>
@@ -11370,7 +11370,7 @@
         <v>78</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>18</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-machine-execution-audit-event.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-machine-execution-audit-event.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$95</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4124" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3665" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -476,7 +476,7 @@
     <t>Cryptographic signature of this log entry</t>
   </si>
   <si>
-    <t>Cryptographic signature or verification hash to ensure the integrity, accountability, and non-repudiation of the AI execution audit log.</t>
+    <t>Provides a digital signature and associated metadata to support verification of the integrity and origin of the AI execution audit record.</t>
   </si>
   <si>
     <t>AuditEvent.modifierExtension</t>
@@ -562,15 +562,6 @@
     <t>This field enables queries of messages by implementation-defined event categories.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/audit-event-type"/&gt;
-    &lt;code value="rest"/&gt;
-    &lt;display value="RESTful Operation"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>Specific type of event.</t>
   </si>
   <si>
@@ -593,9 +584,6 @@
   </si>
   <si>
     <t>This broadly indicates what kind of action was done on the AuditEvent.entity by the AuditEvent.agent.</t>
-  </si>
-  <si>
-    <t>C</t>
   </si>
   <si>
     <t>DICOM Audit Event Action</t>
@@ -644,35 +632,100 @@
     <t>The time or period can be a little arbitrary; where possible, the time should correspond to human assessment of the activity time.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
+    <t>Event.occurrence</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>./effectiveTime[type=IVL_TS]</t>
+  </si>
+  <si>
+    <t>Activity.startTime &amp; Activity.endTime</t>
+  </si>
+  <si>
+    <t>Provenance.occurred[x]</t>
+  </si>
+  <si>
+    <t>AuditEvent.occurred[x].id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Event.occurrence</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>./effectiveTime[type=IVL_TS]</t>
-  </si>
-  <si>
-    <t>Activity.startTime &amp; Activity.endTime</t>
-  </si>
-  <si>
-    <t>Provenance.occurred[x]</t>
-  </si>
-  <si>
-    <t>AuditEvent.occurred[x]:occurredPeriod</t>
-  </si>
-  <si>
-    <t>occurredPeriod</t>
-  </si>
-  <si>
-    <t>Exact execution period (Start/End)</t>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>AuditEvent.occurred[x].extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>AuditEvent.occurred[x].start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>AuditEvent.occurred[x].end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The end value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>./high</t>
   </si>
   <si>
     <t>AuditEvent.recorded</t>
@@ -738,32 +791,7 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>AuditEvent.outcome.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>AuditEvent.outcome.modifierExtension</t>
@@ -1052,7 +1080,7 @@
 </t>
   </si>
   <si>
-    <t>Identifier of who</t>
+    <t>AI system that performed the processing activity</t>
   </si>
   <si>
     <t>Reference to who this agent is that was involved in the event.</t>
@@ -1269,7 +1297,7 @@
 </t>
   </si>
   <si>
-    <t>The identity of source detecting the event</t>
+    <t>AI system that generated this audit record</t>
   </si>
   <si>
     <t>Identifier of the source where the event was detected.</t>
@@ -1312,9 +1340,6 @@
 </t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>Data or objects used</t>
   </si>
   <si>
@@ -1542,156 +1567,93 @@
     <t>Provenance.entity.agent</t>
   </si>
   <si>
-    <t>AuditEvent.entity:inputData</t>
-  </si>
-  <si>
-    <t>inputData</t>
-  </si>
-  <si>
-    <t>Input Data Processed</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:inputData.id</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:inputData.extension</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:inputData.modifierExtension</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:inputData.what</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:inputData.role</t>
+    <t>AuditEvent.entity:referenceDb</t>
+  </si>
+  <si>
+    <t>referenceDb</t>
+  </si>
+  <si>
+    <t>Reference database or knowledge source used by the AI system</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:referenceDb.id</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:referenceDb.extension</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:referenceDb.modifierExtension</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:referenceDb.what</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:referenceDb.role</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/object-role"/&gt;
-    &lt;code value="4"/&gt;
+    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/eu-ai-audit-entity-role"/&gt;
+    &lt;code value="reference-database"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>AuditEvent.entity:inputData.securityLabel</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:inputData.query</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:inputData.detail</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:inputData.detail.id</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:inputData.detail.extension</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:inputData.detail.modifierExtension</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:inputData.detail.type</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:inputData.detail.value[x]</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:inputData.agent</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb</t>
-  </si>
-  <si>
-    <t>referenceDb</t>
-  </si>
-  <si>
-    <t>Identification of specific reference databases or versions (e.g., Clinical Guidelines)</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.id</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.extension</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.modifierExtension</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.what</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.role</t>
+    <t>AuditEvent.entity:referenceDb.securityLabel</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:referenceDb.query</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:referenceDb.detail</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:referenceDb.detail.id</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:referenceDb.detail.extension</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:referenceDb.detail.modifierExtension</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:referenceDb.detail.type</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:referenceDb.detail.value[x]</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:referenceDb.agent</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:outputData</t>
+  </si>
+  <si>
+    <t>outputData</t>
+  </si>
+  <si>
+    <t>A FHIR resource representing an output generated by the AI system during the audited execution</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:outputData.id</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:outputData.extension</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:outputData.modifierExtension</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:outputData.what</t>
+  </si>
+  <si>
+    <t>AuditEvent.entity:outputData.role</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/object-role"/&gt;
-    &lt;code value="17"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.securityLabel</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.query</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.detail</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.detail.id</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.detail.extension</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.detail.modifierExtension</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.detail.type</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.detail.value[x]</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:referenceDb.agent</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:outputData</t>
-  </si>
-  <si>
-    <t>outputData</t>
-  </si>
-  <si>
-    <t>The resulting AI-generated Observation</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:outputData.id</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:outputData.extension</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:outputData.modifierExtension</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:outputData.what</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://example.org/fhir/eu-ai-transparency/StructureDefinition/eu-ai-observation)
-</t>
-  </si>
-  <si>
-    <t>AuditEvent.entity:outputData.role</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/object-role"/&gt;
-    &lt;code value="3"/&gt;
+    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/eu-ai-audit-entity-role"/&gt;
+    &lt;code value="ai-output"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -2029,12 +1991,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP107"/>
+  <dimension ref="A1:AP95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.55859375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="34.24609375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2060,7 +2022,7 @@
     <col min="26" max="26" width="48.51953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3054,7 +3016,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>78</v>
@@ -3172,7 +3134,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>89</v>
@@ -3567,7 +3529,7 @@
         <v>18</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>18</v>
@@ -3585,10 +3547,10 @@
         <v>161</v>
       </c>
       <c r="Y13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>18</v>
@@ -3630,21 +3592,21 @@
         <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>178</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3670,14 +3632,14 @@
         <v>109</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>18</v>
@@ -3687,7 +3649,7 @@
         <v>18</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>18</v>
@@ -3705,10 +3667,10 @@
         <v>113</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>18</v>
@@ -3726,7 +3688,7 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3750,7 +3712,7 @@
         <v>166</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>18</v>
@@ -3761,10 +3723,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3790,13 +3752,13 @@
         <v>109</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3825,10 +3787,10 @@
         <v>113</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>18</v>
@@ -3846,7 +3808,7 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3870,7 +3832,7 @@
         <v>134</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>18</v>
@@ -3881,10 +3843,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3892,7 +3854,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>89</v>
@@ -3907,16 +3869,16 @@
         <v>18</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3954,17 +3916,19 @@
         <v>18</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AC16" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="AD16" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>200</v>
+        <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3979,46 +3943,44 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AL16" t="s" s="2">
+    </row>
+    <row r="17" hidden="true">
+      <c r="A17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AM16" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>18</v>
@@ -4027,17 +3989,15 @@
         <v>18</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>195</v>
+        <v>91</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -4086,7 +4046,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -4095,72 +4055,70 @@
         <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>201</v>
+        <v>18</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>202</v>
+        <v>18</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>205</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="N18" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>18</v>
       </c>
@@ -4196,57 +4154,57 @@
         <v>18</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>215</v>
+        <v>18</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>218</v>
+        <v>18</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>219</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4254,13 +4212,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>18</v>
@@ -4269,20 +4227,18 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>18</v>
       </c>
@@ -4330,7 +4286,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4339,7 +4295,7 @@
         <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>101</v>
@@ -4348,10 +4304,10 @@
         <v>18</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>18</v>
@@ -4363,12 +4319,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4376,35 +4332,39 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q20" s="2"/>
+      <c r="Q20" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="R20" t="s" s="2">
         <v>18</v>
       </c>
@@ -4448,7 +4408,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4457,10 +4417,10 @@
         <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>18</v>
@@ -4469,7 +4429,7 @@
         <v>18</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>18</v>
@@ -4481,46 +4441,48 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>136</v>
+        <v>229</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>18</v>
       </c>
@@ -4568,80 +4530,80 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AP21" t="s" s="2">
-        <v>18</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>239</v>
+        <v>18</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>152</v>
+        <v>243</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>153</v>
+        <v>244</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>18</v>
@@ -4690,28 +4652,28 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>134</v>
+        <v>245</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>18</v>
@@ -4725,10 +4687,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4736,7 +4698,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>89</v>
@@ -4748,23 +4710,19 @@
         <v>18</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>18</v>
       </c>
@@ -4788,13 +4746,13 @@
         <v>18</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>248</v>
+        <v>18</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>249</v>
+        <v>18</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>18</v>
@@ -4812,31 +4770,31 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>18</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>18</v>
@@ -4847,14 +4805,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4870,19 +4828,19 @@
         <v>18</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>252</v>
+        <v>209</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>253</v>
+        <v>210</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>254</v>
+        <v>152</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4908,13 +4866,13 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>256</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -4932,7 +4890,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>212</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4944,16 +4902,16 @@
         <v>18</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>18</v>
@@ -4967,14 +4925,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4987,25 +4945,25 @@
         <v>18</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>261</v>
+        <v>152</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>262</v>
+        <v>153</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>18</v>
@@ -5030,13 +4988,13 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>263</v>
+        <v>18</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>264</v>
+        <v>18</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
@@ -5054,7 +5012,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -5066,33 +5024,33 @@
         <v>18</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>265</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>266</v>
+        <v>18</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>268</v>
+        <v>18</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>269</v>
+        <v>18</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>270</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5100,10 +5058,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>18</v>
@@ -5112,19 +5070,23 @@
         <v>18</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>18</v>
       </c>
@@ -5148,13 +5110,13 @@
         <v>18</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>18</v>
+        <v>258</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>18</v>
+        <v>259</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>18</v>
+        <v>260</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>18</v>
@@ -5172,13 +5134,13 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>18</v>
@@ -5187,19 +5149,19 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>164</v>
+        <v>18</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>266</v>
+        <v>165</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>269</v>
+        <v>18</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>18</v>
@@ -5207,10 +5169,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5221,7 +5183,7 @@
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>18</v>
@@ -5230,21 +5192,21 @@
         <v>18</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>277</v>
+        <v>157</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>18</v>
       </c>
@@ -5268,13 +5230,13 @@
         <v>18</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>18</v>
+        <v>266</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>18</v>
+        <v>267</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>18</v>
@@ -5292,13 +5254,13 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>18</v>
@@ -5307,19 +5269,19 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>281</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>282</v>
+        <v>165</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>283</v>
+        <v>245</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>284</v>
+        <v>18</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>18</v>
@@ -5327,21 +5289,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>18</v>
+        <v>269</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -5350,19 +5312,23 @@
         <v>18</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>286</v>
+        <v>157</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>18</v>
       </c>
@@ -5386,13 +5352,13 @@
         <v>18</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>18</v>
+        <v>274</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>18</v>
+        <v>275</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>18</v>
@@ -5410,13 +5376,13 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>18</v>
@@ -5425,66 +5391,62 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>18</v>
+        <v>279</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>18</v>
+        <v>281</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>290</v>
+        <v>18</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>221</v>
+        <v>283</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>18</v>
       </c>
@@ -5532,10 +5494,10 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>78</v>
@@ -5547,30 +5509,30 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>295</v>
+        <v>164</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>298</v>
+        <v>18</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>300</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5593,16 +5555,18 @@
         <v>18</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>228</v>
+        <v>288</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>229</v>
+        <v>289</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>18</v>
       </c>
@@ -5650,7 +5614,7 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>231</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5659,25 +5623,25 @@
         <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>18</v>
+        <v>292</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>18</v>
+        <v>293</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>18</v>
+        <v>295</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>18</v>
@@ -5685,21 +5649,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>18</v>
@@ -5711,17 +5675,15 @@
         <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>136</v>
+        <v>297</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>235</v>
+        <v>298</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>18</v>
@@ -5770,80 +5732,80 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>18</v>
+        <v>277</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>18</v>
+        <v>280</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>239</v>
+        <v>301</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>240</v>
+        <v>302</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>241</v>
+        <v>303</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>152</v>
+        <v>304</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>153</v>
+        <v>305</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -5892,10 +5854,10 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>242</v>
+        <v>300</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>78</v>
@@ -5904,33 +5866,33 @@
         <v>18</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>18</v>
+        <v>306</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>18</v>
+        <v>307</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>134</v>
+        <v>308</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>18</v>
+        <v>309</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>18</v>
+        <v>310</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>18</v>
+        <v>311</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5953,20 +5915,16 @@
         <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>203</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>18</v>
       </c>
@@ -5990,13 +5948,13 @@
         <v>18</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>309</v>
+        <v>18</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>310</v>
+        <v>18</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>18</v>
@@ -6014,7 +5972,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>205</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -6023,40 +5981,40 @@
         <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>311</v>
+        <v>18</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>296</v>
+        <v>18</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>312</v>
+        <v>207</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>313</v>
+        <v>18</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>314</v>
+        <v>18</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>315</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6075,20 +6033,18 @@
         <v>18</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>209</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>318</v>
+        <v>210</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>18</v>
       </c>
@@ -6112,13 +6068,13 @@
         <v>18</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>321</v>
+        <v>18</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>322</v>
+        <v>18</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>18</v>
@@ -6136,7 +6092,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>316</v>
+        <v>212</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -6148,68 +6104,68 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>296</v>
+        <v>18</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>323</v>
+        <v>207</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>324</v>
+        <v>18</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>314</v>
+        <v>18</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>325</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>327</v>
+        <v>250</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>328</v>
+        <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>329</v>
+        <v>251</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>330</v>
+        <v>252</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>331</v>
+        <v>152</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>332</v>
+        <v>153</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>18</v>
@@ -6258,45 +6214,45 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>326</v>
+        <v>253</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>333</v>
+        <v>18</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>296</v>
+        <v>18</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>334</v>
+        <v>134</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>335</v>
+        <v>18</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>336</v>
+        <v>18</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>337</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6316,34 +6272,32 @@
         <v>18</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>339</v>
+        <v>157</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>343</v>
+        <v>319</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q36" t="s" s="2">
-        <v>32</v>
-      </c>
+      <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
         <v>18</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>18</v>
@@ -6358,13 +6312,13 @@
         <v>18</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>18</v>
+        <v>258</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>18</v>
+        <v>321</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>18</v>
@@ -6382,7 +6336,7 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6397,30 +6351,30 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>18</v>
+        <v>322</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>18</v>
+        <v>325</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>18</v>
+        <v>326</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6431,7 +6385,7 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>18</v>
@@ -6443,16 +6397,20 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>347</v>
+        <v>157</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>18</v>
       </c>
@@ -6476,13 +6434,13 @@
         <v>18</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>18</v>
+        <v>332</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>18</v>
+        <v>333</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>18</v>
@@ -6500,13 +6458,13 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>18</v>
@@ -6515,41 +6473,41 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>350</v>
+        <v>18</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>18</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>353</v>
+        <v>325</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>354</v>
+        <v>336</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>18</v>
+        <v>338</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>18</v>
@@ -6558,22 +6516,22 @@
         <v>18</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>339</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>18</v>
@@ -6622,13 +6580,13 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>18</v>
@@ -6637,30 +6595,30 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>18</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>18</v>
+        <v>347</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6680,27 +6638,29 @@
         <v>18</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q39" s="2"/>
+      <c r="Q39" t="s" s="2">
+        <v>32</v>
+      </c>
       <c r="R39" t="s" s="2">
         <v>18</v>
       </c>
@@ -6744,7 +6704,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6762,16 +6722,16 @@
         <v>18</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>371</v>
+        <v>18</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>18</v>
@@ -6779,21 +6739,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>373</v>
+        <v>18</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>18</v>
@@ -6805,20 +6765,16 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>157</v>
+        <v>358</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>18</v>
       </c>
@@ -6842,13 +6798,13 @@
         <v>18</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>376</v>
+        <v>18</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>264</v>
+        <v>18</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>18</v>
@@ -6866,13 +6822,13 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>18</v>
@@ -6881,30 +6837,30 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>18</v>
+        <v>361</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>266</v>
+        <v>362</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>18</v>
+        <v>365</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6912,34 +6868,34 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>18</v>
@@ -6988,13 +6944,13 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>18</v>
@@ -7006,27 +6962,27 @@
         <v>18</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>384</v>
+        <v>277</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>18</v>
+        <v>373</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7049,16 +7005,20 @@
         <v>18</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>228</v>
+        <v>375</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>229</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>18</v>
       </c>
@@ -7106,7 +7066,7 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>231</v>
+        <v>374</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -7115,25 +7075,25 @@
         <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>18</v>
+        <v>362</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>233</v>
+        <v>380</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>18</v>
+        <v>381</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>18</v>
+        <v>382</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>18</v>
@@ -7141,14 +7101,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>149</v>
+        <v>384</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7167,18 +7127,20 @@
         <v>18</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>235</v>
+        <v>385</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>18</v>
       </c>
@@ -7202,13 +7164,13 @@
         <v>18</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>18</v>
+        <v>387</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>18</v>
+        <v>275</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>18</v>
@@ -7226,7 +7188,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>237</v>
+        <v>383</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -7238,68 +7200,68 @@
         <v>18</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>18</v>
+        <v>277</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>233</v>
+        <v>388</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>18</v>
+        <v>389</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>239</v>
+        <v>18</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>240</v>
+        <v>391</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>241</v>
+        <v>392</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>152</v>
+        <v>393</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>153</v>
+        <v>394</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>18</v>
@@ -7348,31 +7310,31 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>242</v>
+        <v>390</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>18</v>
+        <v>395</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>134</v>
+        <v>396</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>18</v>
+        <v>397</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7383,10 +7345,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7409,18 +7371,16 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>347</v>
+        <v>247</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>391</v>
+        <v>203</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>392</v>
+        <v>204</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>393</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>18</v>
       </c>
@@ -7468,7 +7428,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>390</v>
+        <v>205</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7477,22 +7437,22 @@
         <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>384</v>
+        <v>18</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>394</v>
+        <v>207</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>395</v>
+        <v>18</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>18</v>
@@ -7503,21 +7463,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>397</v>
+        <v>149</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>18</v>
@@ -7526,21 +7486,21 @@
         <v>18</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>328</v>
+        <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>398</v>
+        <v>209</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>18</v>
       </c>
@@ -7588,31 +7548,31 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>396</v>
+        <v>212</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>384</v>
+        <v>18</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>334</v>
+        <v>207</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>401</v>
+        <v>18</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>18</v>
@@ -7623,14 +7583,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7643,23 +7603,25 @@
         <v>18</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>403</v>
+        <v>251</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>405</v>
+        <v>153</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
@@ -7684,13 +7646,13 @@
         <v>18</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>406</v>
+        <v>18</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>407</v>
+        <v>18</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>18</v>
@@ -7708,7 +7670,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>402</v>
+        <v>253</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7720,19 +7682,19 @@
         <v>18</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>384</v>
+        <v>18</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>408</v>
+        <v>134</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>409</v>
+        <v>18</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>18</v>
@@ -7743,21 +7705,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>411</v>
+        <v>18</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>412</v>
+        <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>18</v>
@@ -7766,22 +7728,20 @@
         <v>18</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>221</v>
+        <v>358</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>18</v>
@@ -7818,23 +7778,25 @@
         <v>18</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AC48" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="AD48" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>18</v>
@@ -7846,35 +7808,35 @@
         <v>18</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>165</v>
+        <v>395</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>420</v>
+        <v>18</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>18</v>
+        <v>408</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>89</v>
@@ -7886,19 +7848,21 @@
         <v>18</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>228</v>
+        <v>339</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>229</v>
+        <v>409</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>230</v>
+        <v>410</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>18</v>
       </c>
@@ -7946,31 +7910,31 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>231</v>
+        <v>407</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>18</v>
+        <v>395</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>233</v>
+        <v>345</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>18</v>
+        <v>412</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>18</v>
@@ -7981,14 +7945,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8007,18 +7971,18 @@
         <v>18</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>235</v>
+        <v>414</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>18</v>
       </c>
@@ -8042,13 +8006,13 @@
         <v>18</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>18</v>
+        <v>258</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>18</v>
+        <v>417</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>18</v>
+        <v>418</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>18</v>
@@ -8066,7 +8030,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>237</v>
+        <v>413</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -8078,19 +8042,19 @@
         <v>18</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>18</v>
+        <v>395</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>233</v>
+        <v>419</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>18</v>
+        <v>420</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
@@ -8101,18 +8065,18 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>239</v>
+        <v>422</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>78</v>
@@ -8121,25 +8085,25 @@
         <v>18</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>240</v>
+        <v>423</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>241</v>
+        <v>424</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>152</v>
+        <v>425</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>153</v>
+        <v>426</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -8176,19 +8140,17 @@
         <v>18</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>242</v>
+        <v>421</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -8200,33 +8162,33 @@
         <v>18</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>134</v>
+        <v>428</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>18</v>
+        <v>429</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>18</v>
+        <v>430</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>18</v>
+        <v>431</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8246,20 +8208,18 @@
         <v>18</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>426</v>
+        <v>247</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>427</v>
+        <v>203</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>18</v>
@@ -8308,7 +8268,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>425</v>
+        <v>205</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -8317,47 +8277,47 @@
         <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>334</v>
+        <v>207</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>430</v>
+        <v>18</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>431</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>18</v>
@@ -8369,18 +8329,18 @@
         <v>18</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>433</v>
+        <v>209</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>18</v>
       </c>
@@ -8404,13 +8364,13 @@
         <v>18</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>436</v>
+        <v>18</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>437</v>
+        <v>18</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>18</v>
@@ -8428,34 +8388,34 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>432</v>
+        <v>212</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>439</v>
+        <v>207</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>440</v>
+        <v>18</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>441</v>
+        <v>18</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>18</v>
@@ -8463,14 +8423,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8483,25 +8443,25 @@
         <v>18</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>443</v>
+        <v>251</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>444</v>
+        <v>252</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>445</v>
+        <v>152</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>446</v>
+        <v>153</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>18</v>
@@ -8526,13 +8486,13 @@
         <v>18</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>447</v>
+        <v>18</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>448</v>
+        <v>18</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>18</v>
@@ -8550,7 +8510,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>442</v>
+        <v>253</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8562,19 +8522,19 @@
         <v>18</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>449</v>
+        <v>134</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>450</v>
+        <v>18</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>18</v>
@@ -8585,10 +8545,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8611,20 +8571,18 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>18</v>
       </c>
@@ -8672,7 +8630,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8690,27 +8648,27 @@
         <v>18</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>438</v>
+        <v>165</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>457</v>
+        <v>345</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>18</v>
+        <v>441</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8721,7 +8679,7 @@
         <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>18</v>
@@ -8733,17 +8691,17 @@
         <v>18</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
@@ -8768,13 +8726,13 @@
         <v>18</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>18</v>
+        <v>446</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>18</v>
+        <v>447</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>18</v>
@@ -8792,13 +8750,13 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>18</v>
@@ -8810,16 +8768,16 @@
         <v>18</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>18</v>
+        <v>451</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>18</v>
@@ -8827,10 +8785,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8841,7 +8799,7 @@
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>18</v>
@@ -8853,16 +8811,20 @@
         <v>18</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>229</v>
+        <v>453</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>18</v>
       </c>
@@ -8886,13 +8848,13 @@
         <v>18</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>18</v>
+        <v>457</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>18</v>
+        <v>458</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>18</v>
@@ -8910,31 +8872,31 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>231</v>
+        <v>452</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>233</v>
+        <v>459</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>18</v>
+        <v>460</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>18</v>
@@ -8945,21 +8907,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>18</v>
@@ -8968,21 +8930,23 @@
         <v>18</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>136</v>
+        <v>462</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>235</v>
+        <v>463</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>236</v>
+        <v>464</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
       </c>
@@ -9030,31 +8994,31 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>237</v>
+        <v>461</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>233</v>
+        <v>467</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>18</v>
+        <v>468</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>18</v>
@@ -9065,14 +9029,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>239</v>
+        <v>18</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9085,25 +9049,23 @@
         <v>18</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>240</v>
+        <v>470</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>153</v>
+        <v>472</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
@@ -9152,7 +9114,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>242</v>
+        <v>469</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -9164,19 +9126,19 @@
         <v>18</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>134</v>
+        <v>473</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>18</v>
+        <v>474</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
@@ -9187,10 +9149,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9198,7 +9160,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>89</v>
@@ -9213,13 +9175,13 @@
         <v>18</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>469</v>
+        <v>203</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>470</v>
+        <v>204</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9246,13 +9208,13 @@
         <v>18</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>471</v>
+        <v>18</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>18</v>
@@ -9270,31 +9232,31 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>468</v>
+        <v>205</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>408</v>
+        <v>207</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>472</v>
+        <v>18</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>18</v>
@@ -9305,21 +9267,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>18</v>
@@ -9331,18 +9293,18 @@
         <v>18</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>474</v>
+        <v>136</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>475</v>
+        <v>209</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>18</v>
       </c>
@@ -9390,31 +9352,31 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>473</v>
+        <v>212</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>478</v>
+        <v>207</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>479</v>
+        <v>18</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>18</v>
@@ -9425,14 +9387,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9445,24 +9407,26 @@
         <v>18</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>481</v>
+        <v>251</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>482</v>
+        <v>252</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>18</v>
       </c>
@@ -9510,7 +9474,7 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>480</v>
+        <v>253</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9522,7 +9486,7 @@
         <v>18</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>18</v>
@@ -9531,62 +9495,56 @@
         <v>18</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>484</v>
+        <v>134</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>485</v>
+        <v>18</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>486</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>411</v>
+        <v>18</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>89</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>18</v>
       </c>
@@ -9610,13 +9568,13 @@
         <v>18</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>18</v>
+        <v>481</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>18</v>
@@ -9634,13 +9592,13 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>410</v>
+        <v>478</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>18</v>
@@ -9652,27 +9610,27 @@
         <v>18</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>165</v>
+        <v>448</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>419</v>
+        <v>482</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>420</v>
+        <v>18</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>422</v>
+        <v>483</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9680,7 +9638,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>89</v>
@@ -9695,16 +9653,18 @@
         <v>18</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>228</v>
+        <v>484</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>229</v>
+        <v>485</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>230</v>
+        <v>486</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>18</v>
       </c>
@@ -9752,31 +9712,31 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>231</v>
+        <v>483</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>233</v>
+        <v>488</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>18</v>
+        <v>489</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>18</v>
@@ -9787,14 +9747,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>423</v>
+        <v>490</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9813,16 +9773,16 @@
         <v>18</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>235</v>
+        <v>491</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>236</v>
+        <v>492</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>152</v>
+        <v>493</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9872,7 +9832,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>237</v>
+        <v>490</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9884,7 +9844,7 @@
         <v>18</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>18</v>
@@ -9893,28 +9853,30 @@
         <v>18</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>233</v>
+        <v>494</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>18</v>
+        <v>495</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>18</v>
+        <v>496</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="D66" t="s" s="2">
-        <v>239</v>
+        <v>422</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9924,28 +9886,28 @@
         <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>240</v>
+        <v>499</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>241</v>
+        <v>424</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>152</v>
+        <v>425</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>153</v>
+        <v>426</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>18</v>
@@ -9994,7 +9956,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>242</v>
+        <v>421</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -10006,33 +9968,33 @@
         <v>18</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>134</v>
+        <v>428</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>18</v>
+        <v>429</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>18</v>
+        <v>430</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>18</v>
+        <v>431</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10052,20 +10014,18 @@
         <v>18</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>426</v>
+        <v>247</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>427</v>
+        <v>203</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>18</v>
@@ -10114,7 +10074,7 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>425</v>
+        <v>205</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -10123,47 +10083,47 @@
         <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>334</v>
+        <v>207</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>430</v>
+        <v>18</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>431</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>18</v>
@@ -10175,18 +10135,18 @@
         <v>18</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>433</v>
+        <v>209</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>18</v>
       </c>
@@ -10195,7 +10155,7 @@
         <v>18</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>495</v>
+        <v>18</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>18</v>
@@ -10210,13 +10170,13 @@
         <v>18</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>436</v>
+        <v>18</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>437</v>
+        <v>18</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>18</v>
@@ -10234,34 +10194,34 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>432</v>
+        <v>212</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>439</v>
+        <v>207</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>440</v>
+        <v>18</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>441</v>
+        <v>18</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>18</v>
@@ -10269,14 +10229,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10289,25 +10249,25 @@
         <v>18</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>443</v>
+        <v>251</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>444</v>
+        <v>252</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>445</v>
+        <v>152</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>446</v>
+        <v>153</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>18</v>
@@ -10332,13 +10292,13 @@
         <v>18</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>447</v>
+        <v>18</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>448</v>
+        <v>18</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>18</v>
@@ -10356,7 +10316,7 @@
         <v>18</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>442</v>
+        <v>253</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -10368,19 +10328,19 @@
         <v>18</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>449</v>
+        <v>134</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>450</v>
+        <v>18</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>18</v>
@@ -10391,10 +10351,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10402,7 +10362,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>89</v>
@@ -10417,20 +10377,18 @@
         <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>18</v>
       </c>
@@ -10478,7 +10436,7 @@
         <v>18</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -10496,27 +10454,27 @@
         <v>18</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>438</v>
+        <v>165</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>457</v>
+        <v>345</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>18</v>
+        <v>441</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10524,10 +10482,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>18</v>
@@ -10539,17 +10497,17 @@
         <v>18</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>18</v>
@@ -10559,7 +10517,7 @@
         <v>18</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>18</v>
+        <v>505</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>18</v>
@@ -10574,13 +10532,13 @@
         <v>18</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>18</v>
+        <v>446</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>18</v>
+        <v>447</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>18</v>
@@ -10598,13 +10556,13 @@
         <v>18</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>18</v>
@@ -10616,16 +10574,16 @@
         <v>18</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>18</v>
+        <v>451</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>18</v>
@@ -10633,10 +10591,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10647,7 +10605,7 @@
         <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>18</v>
@@ -10659,16 +10617,20 @@
         <v>18</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>229</v>
+        <v>453</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>18</v>
       </c>
@@ -10692,13 +10654,13 @@
         <v>18</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>18</v>
+        <v>457</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>18</v>
+        <v>458</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>18</v>
@@ -10716,31 +10678,31 @@
         <v>18</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>231</v>
+        <v>452</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>233</v>
+        <v>459</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>18</v>
+        <v>460</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>18</v>
@@ -10751,21 +10713,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>18</v>
@@ -10774,21 +10736,23 @@
         <v>18</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>136</v>
+        <v>462</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>235</v>
+        <v>463</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>236</v>
+        <v>464</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>18</v>
       </c>
@@ -10836,31 +10800,31 @@
         <v>18</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>237</v>
+        <v>461</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>233</v>
+        <v>467</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>18</v>
+        <v>468</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>18</v>
@@ -10871,14 +10835,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>239</v>
+        <v>18</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10891,25 +10855,23 @@
         <v>18</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>240</v>
+        <v>470</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>153</v>
+        <v>472</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>18</v>
@@ -10958,7 +10920,7 @@
         <v>18</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>242</v>
+        <v>469</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10970,19 +10932,19 @@
         <v>18</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>134</v>
+        <v>473</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>18</v>
+        <v>474</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>18</v>
@@ -10993,10 +10955,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11004,7 +10966,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>89</v>
@@ -11019,13 +10981,13 @@
         <v>18</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>469</v>
+        <v>203</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>470</v>
+        <v>204</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11052,13 +11014,13 @@
         <v>18</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>471</v>
+        <v>18</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>18</v>
@@ -11076,31 +11038,31 @@
         <v>18</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>468</v>
+        <v>205</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>408</v>
+        <v>207</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>472</v>
+        <v>18</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>18</v>
@@ -11111,21 +11073,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>18</v>
@@ -11137,18 +11099,18 @@
         <v>18</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>474</v>
+        <v>136</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>475</v>
+        <v>209</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>18</v>
       </c>
@@ -11196,31 +11158,31 @@
         <v>18</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>473</v>
+        <v>212</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>478</v>
+        <v>207</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>479</v>
+        <v>18</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>18</v>
@@ -11231,14 +11193,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11251,24 +11213,26 @@
         <v>18</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>481</v>
+        <v>251</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>482</v>
+        <v>252</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>18</v>
       </c>
@@ -11316,7 +11280,7 @@
         <v>18</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>480</v>
+        <v>253</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -11328,7 +11292,7 @@
         <v>18</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>18</v>
@@ -11337,37 +11301,35 @@
         <v>18</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>484</v>
+        <v>134</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>485</v>
+        <v>18</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>486</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>411</v>
+        <v>18</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>18</v>
@@ -11376,23 +11338,19 @@
         <v>18</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>507</v>
+        <v>479</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>18</v>
       </c>
@@ -11416,13 +11374,13 @@
         <v>18</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>18</v>
+        <v>481</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>18</v>
@@ -11440,13 +11398,13 @@
         <v>18</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>410</v>
+        <v>478</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>18</v>
@@ -11458,27 +11416,27 @@
         <v>18</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>165</v>
+        <v>448</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>419</v>
+        <v>482</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>420</v>
+        <v>18</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>422</v>
+        <v>483</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11486,7 +11444,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>89</v>
@@ -11501,16 +11459,18 @@
         <v>18</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>228</v>
+        <v>484</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>229</v>
+        <v>485</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>230</v>
+        <v>486</v>
       </c>
       <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>18</v>
       </c>
@@ -11558,31 +11518,31 @@
         <v>18</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>231</v>
+        <v>483</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>233</v>
+        <v>488</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>18</v>
+        <v>489</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>18</v>
@@ -11593,14 +11553,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>423</v>
+        <v>490</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11619,16 +11579,16 @@
         <v>18</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>235</v>
+        <v>491</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>236</v>
+        <v>492</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>152</v>
+        <v>493</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11678,7 +11638,7 @@
         <v>18</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>237</v>
+        <v>490</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11690,7 +11650,7 @@
         <v>18</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>18</v>
@@ -11699,59 +11659,61 @@
         <v>18</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>233</v>
+        <v>494</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>18</v>
+        <v>495</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>18</v>
+        <v>496</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C81" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="D81" t="s" s="2">
-        <v>239</v>
+        <v>422</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J81" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>240</v>
+        <v>517</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>241</v>
+        <v>424</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>152</v>
+        <v>425</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>153</v>
+        <v>426</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>18</v>
@@ -11800,7 +11762,7 @@
         <v>18</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>242</v>
+        <v>421</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -11812,33 +11774,33 @@
         <v>18</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>134</v>
+        <v>428</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>18</v>
+        <v>429</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>18</v>
+        <v>430</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>18</v>
+        <v>431</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11858,20 +11820,18 @@
         <v>18</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>426</v>
+        <v>247</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>427</v>
+        <v>203</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>18</v>
@@ -11920,7 +11880,7 @@
         <v>18</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>425</v>
+        <v>205</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11929,47 +11889,47 @@
         <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>334</v>
+        <v>207</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>430</v>
+        <v>18</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>431</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>18</v>
@@ -11981,18 +11941,18 @@
         <v>18</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>433</v>
+        <v>209</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>18</v>
       </c>
@@ -12001,7 +11961,7 @@
         <v>18</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>513</v>
+        <v>18</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>18</v>
@@ -12016,13 +11976,13 @@
         <v>18</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>436</v>
+        <v>18</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>437</v>
+        <v>18</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>18</v>
@@ -12040,34 +12000,34 @@
         <v>18</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>432</v>
+        <v>212</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>439</v>
+        <v>207</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>440</v>
+        <v>18</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>441</v>
+        <v>18</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>18</v>
@@ -12075,14 +12035,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12095,25 +12055,25 @@
         <v>18</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>443</v>
+        <v>251</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>444</v>
+        <v>252</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>445</v>
+        <v>152</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>446</v>
+        <v>153</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>18</v>
@@ -12138,13 +12098,13 @@
         <v>18</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>447</v>
+        <v>18</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>448</v>
+        <v>18</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>18</v>
@@ -12162,7 +12122,7 @@
         <v>18</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>442</v>
+        <v>253</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -12174,19 +12134,19 @@
         <v>18</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>449</v>
+        <v>134</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>450</v>
+        <v>18</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>18</v>
@@ -12197,10 +12157,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12208,7 +12168,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>89</v>
@@ -12223,20 +12183,18 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>18</v>
       </c>
@@ -12284,7 +12242,7 @@
         <v>18</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -12302,27 +12260,27 @@
         <v>18</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>438</v>
+        <v>165</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>457</v>
+        <v>345</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>18</v>
+        <v>441</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12330,10 +12288,10 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>18</v>
@@ -12345,17 +12303,17 @@
         <v>18</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>18</v>
@@ -12365,7 +12323,7 @@
         <v>18</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>18</v>
+        <v>523</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>18</v>
@@ -12380,13 +12338,13 @@
         <v>18</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>18</v>
+        <v>446</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>18</v>
+        <v>447</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>18</v>
@@ -12404,13 +12362,13 @@
         <v>18</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>18</v>
@@ -12422,16 +12380,16 @@
         <v>18</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>18</v>
+        <v>451</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>18</v>
@@ -12439,10 +12397,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12453,7 +12411,7 @@
         <v>77</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>18</v>
@@ -12465,16 +12423,20 @@
         <v>18</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>229</v>
+        <v>453</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>18</v>
       </c>
@@ -12498,13 +12460,13 @@
         <v>18</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>18</v>
+        <v>457</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>18</v>
+        <v>458</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>18</v>
@@ -12522,31 +12484,31 @@
         <v>18</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>231</v>
+        <v>452</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>233</v>
+        <v>459</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>18</v>
+        <v>460</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>18</v>
@@ -12557,21 +12519,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>18</v>
@@ -12580,21 +12542,23 @@
         <v>18</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>136</v>
+        <v>462</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>235</v>
+        <v>463</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>236</v>
+        <v>464</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>18</v>
       </c>
@@ -12642,31 +12606,31 @@
         <v>18</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>237</v>
+        <v>461</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>233</v>
+        <v>467</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>18</v>
+        <v>468</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>18</v>
@@ -12677,14 +12641,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>239</v>
+        <v>18</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12697,25 +12661,23 @@
         <v>18</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>240</v>
+        <v>470</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>153</v>
+        <v>472</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>18</v>
@@ -12764,7 +12726,7 @@
         <v>18</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>242</v>
+        <v>469</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12776,19 +12738,19 @@
         <v>18</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>134</v>
+        <v>473</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>18</v>
+        <v>474</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>18</v>
@@ -12799,10 +12761,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12810,7 +12772,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>89</v>
@@ -12825,13 +12787,13 @@
         <v>18</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>469</v>
+        <v>203</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>470</v>
+        <v>204</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12858,13 +12820,13 @@
         <v>18</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>471</v>
+        <v>18</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>18</v>
@@ -12882,31 +12844,31 @@
         <v>18</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>468</v>
+        <v>205</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>408</v>
+        <v>207</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>472</v>
+        <v>18</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>18</v>
@@ -12917,21 +12879,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>18</v>
@@ -12943,18 +12905,18 @@
         <v>18</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>474</v>
+        <v>136</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>475</v>
+        <v>209</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>18</v>
       </c>
@@ -13002,31 +12964,31 @@
         <v>18</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>473</v>
+        <v>212</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>478</v>
+        <v>207</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>479</v>
+        <v>18</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>18</v>
@@ -13037,14 +12999,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13057,24 +13019,26 @@
         <v>18</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>481</v>
+        <v>251</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>482</v>
+        <v>252</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>18</v>
       </c>
@@ -13122,7 +13086,7 @@
         <v>18</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>480</v>
+        <v>253</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
@@ -13134,7 +13098,7 @@
         <v>18</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>18</v>
@@ -13143,62 +13107,56 @@
         <v>18</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>484</v>
+        <v>134</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>485</v>
+        <v>18</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>486</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>411</v>
+        <v>18</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>89</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>525</v>
+        <v>479</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>18</v>
       </c>
@@ -13222,13 +13180,13 @@
         <v>18</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>18</v>
+        <v>481</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>18</v>
@@ -13246,13 +13204,13 @@
         <v>18</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>410</v>
+        <v>478</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>18</v>
@@ -13264,27 +13222,27 @@
         <v>18</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>165</v>
+        <v>448</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>419</v>
+        <v>482</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>420</v>
+        <v>18</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>422</v>
+        <v>483</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13292,7 +13250,7 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>89</v>
@@ -13307,16 +13265,18 @@
         <v>18</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>228</v>
+        <v>484</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>229</v>
+        <v>485</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>230</v>
+        <v>486</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>18</v>
       </c>
@@ -13364,31 +13324,31 @@
         <v>18</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>231</v>
+        <v>483</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>233</v>
+        <v>488</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>18</v>
+        <v>489</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>18</v>
@@ -13399,14 +13359,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>423</v>
+        <v>490</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13425,16 +13385,16 @@
         <v>18</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>235</v>
+        <v>491</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>236</v>
+        <v>492</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>152</v>
+        <v>493</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13484,7 +13444,7 @@
         <v>18</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>237</v>
+        <v>490</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -13496,7 +13456,7 @@
         <v>18</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>18</v>
@@ -13505,1464 +13465,20 @@
         <v>18</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>233</v>
+        <v>494</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>18</v>
+        <v>495</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="P96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
-      <c r="P102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O103" s="2"/>
-      <c r="P103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="P104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>486</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP107">
+  <autoFilter ref="A1:AP95">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14972,7 +13488,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI106">
+  <conditionalFormatting sqref="A2:AI94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-machine-execution-audit-event.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-machine-execution-audit-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-machine-execution-audit-event.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-machine-execution-audit-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-machine-execution-audit-event.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-machine-execution-audit-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
